--- a/Template.xlsx
+++ b/Template.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38F4F467-26EE-46B1-8C3B-352B519053B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EAE2E33-C8B5-4467-BAA7-AEF240264157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="713" activeTab="31" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="713" firstSheet="7" activeTab="31" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId1"/>
@@ -41,12 +41,15 @@
     <sheet name="31" sheetId="31" r:id="rId31"/>
     <sheet name="Summary" sheetId="32" r:id="rId32"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId33"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="50">
   <si>
     <t>Daily Production Report</t>
   </si>
@@ -136,6 +139,66 @@
   </si>
   <si>
     <t>Cumulative</t>
+  </si>
+  <si>
+    <t>BD Production</t>
+  </si>
+  <si>
+    <t>BD Engineering</t>
+  </si>
+  <si>
+    <t>Machine Settings</t>
+  </si>
+  <si>
+    <t>Cycle time deviation</t>
+  </si>
+  <si>
+    <t>Absenteeism</t>
+  </si>
+  <si>
+    <t>Power Failure</t>
+  </si>
+  <si>
+    <t>Early leave</t>
+  </si>
+  <si>
+    <t>Mold Change Delay</t>
+  </si>
+  <si>
+    <t>Quality issues</t>
+  </si>
+  <si>
+    <t>Sampling</t>
+  </si>
+  <si>
+    <t>Machine Starting Delay</t>
+  </si>
+  <si>
+    <t>Labor Shortage</t>
+  </si>
+  <si>
+    <t>Color Changing</t>
+  </si>
+  <si>
+    <t>Mold Breakdown</t>
+  </si>
+  <si>
+    <t>Hopper material stock taking</t>
+  </si>
+  <si>
+    <t>No Orders</t>
+  </si>
+  <si>
+    <t>Lack of Materials</t>
+  </si>
+  <si>
+    <t>Material Issues</t>
+  </si>
+  <si>
+    <t>Lack of Packing Materials</t>
+  </si>
+  <si>
+    <t>Others</t>
   </si>
 </sst>
 </file>
@@ -231,7 +294,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -250,14 +313,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -274,6 +340,1784 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2000" b="1" i="0" u="none" strike="noStrike" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="333333"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="Calibri"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="2000" b="1">
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:rPr>
+              <a:t>IM</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="2000" b="1" baseline="0">
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:rPr>
+              <a:t> Breakdown Analysis</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" sz="2000" b="1">
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.2361383629635286E-2"/>
+          <c:y val="0.10750724637681161"/>
+          <c:w val="0.88320974441301636"/>
+          <c:h val="0.55653771539427133"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Summary!$B$17</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>KG</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4F81BD"/>
+            </a:solidFill>
+            <a:ln w="25400">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Summary!$A$18:$A$37</c:f>
+              <c:strCache>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>BD Production</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>BD Engineering</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Machine Settings</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Cycle time deviation</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Absenteeism</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Power Failure</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Early leave</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Mold Change Delay</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Quality issues</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Sampling</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Machine Starting Delay</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Labor Shortage</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Color Changing</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Mold Breakdown</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Hopper material stock taking</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>No Orders</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Lack of Materials</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Material Issues</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Lack of Packing Materials</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Others</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Summary!$B$18:$B$37</c:f>
+              <c:numCache>
+                <c:formatCode>0.#</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-96B3-440F-9481-63B387C3A96A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="574205776"/>
+        <c:axId val="1"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Summary!$D$17</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Cumulative</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Summary!$A$18:$A$37</c:f>
+              <c:strCache>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>BD Production</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>BD Engineering</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Machine Settings</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Cycle time deviation</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Absenteeism</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Power Failure</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Early leave</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Mold Change Delay</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Quality issues</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Sampling</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Machine Starting Delay</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Labor Shortage</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Color Changing</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Mold Breakdown</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Hopper material stock taking</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>No Orders</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Lack of Materials</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Material Issues</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Lack of Packing Materials</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Others</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Summary!$D$18:$D$37</c:f>
+              <c:numCache>
+                <c:formatCode>0.#%</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-96B3-440F-9481-63B387C3A96A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="3"/>
+        <c:axId val="4"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="574205776"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="333333"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+                <a:cs typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.#" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9525">
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="0" vert="horz"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="333333"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+                <a:cs typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="574205776"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="3"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="4"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="4"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="0.#%" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9525">
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="0" vert="horz"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="333333"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+                <a:cs typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="3"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.39025090395169137"/>
+          <c:y val="0.92765920574707428"/>
+          <c:w val="0.33005419777073319"/>
+          <c:h val="5.6985707880564833E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="333333"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:latin typeface="Calibri"/>
+          <a:ea typeface="Calibri"/>
+          <a:cs typeface="Calibri"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2000" b="1" i="0" u="none" strike="noStrike" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="333333"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="Calibri"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="2000" b="1">
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:rPr>
+              <a:t>BM</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="2000" b="1" baseline="0">
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:rPr>
+              <a:t> Breakdown Analysis</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" sz="2000" b="1">
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.2361383629635286E-2"/>
+          <c:y val="0.10750724637681161"/>
+          <c:w val="0.88320974441301636"/>
+          <c:h val="0.55653771539427133"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Summary!$B$41</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>KG</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4F81BD"/>
+            </a:solidFill>
+            <a:ln w="25400">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Summary!$A$42:$A$61</c:f>
+              <c:strCache>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>BD Production</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>BD Engineering</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Machine Settings</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Cycle time deviation</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Absenteeism</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Power Failure</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Early leave</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Mold Change Delay</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Quality issues</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Sampling</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Machine Starting Delay</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Labor Shortage</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Color Changing</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Mold Breakdown</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Hopper material stock taking</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>No Orders</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Lack of Materials</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Material Issues</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Lack of Packing Materials</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Others</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Summary!$B$42:$B$61</c:f>
+              <c:numCache>
+                <c:formatCode>0.#</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-96B3-440F-9481-63B387C3A96A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="574205776"/>
+        <c:axId val="1"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Summary!$D$41</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Cumulative</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Summary!$A$42:$A$61</c:f>
+              <c:strCache>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>BD Production</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>BD Engineering</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Machine Settings</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Cycle time deviation</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Absenteeism</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Power Failure</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Early leave</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Mold Change Delay</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Quality issues</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Sampling</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Machine Starting Delay</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Labor Shortage</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Color Changing</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Mold Breakdown</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Hopper material stock taking</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>No Orders</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Lack of Materials</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Material Issues</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Lack of Packing Materials</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Others</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Summary!$D$42:$D$61</c:f>
+              <c:numCache>
+                <c:formatCode>0.#%</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-96B3-440F-9481-63B387C3A96A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="3"/>
+        <c:axId val="4"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="574205776"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="333333"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+                <a:cs typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.#" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9525">
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="0" vert="horz"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="333333"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+                <a:cs typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="574205776"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="3"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="4"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="4"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="0.#%" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9525">
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="0" vert="horz"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="333333"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+                <a:cs typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="3"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.39025090395169137"/>
+          <c:y val="0.92765920574707428"/>
+          <c:w val="0.33005419777073319"/>
+          <c:h val="5.6985707880564833E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="333333"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:latin typeface="Calibri"/>
+          <a:ea typeface="Calibri"/>
+          <a:cs typeface="Calibri"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{880A6214-7F69-4EB2-90A2-145C49D1B25D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADEE5DC5-DE5F-2418-EB42-39098F68D357}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Summery"/>
+      <sheetName val="1"/>
+      <sheetName val="2"/>
+      <sheetName val="3"/>
+      <sheetName val="4"/>
+      <sheetName val="5"/>
+      <sheetName val="6"/>
+      <sheetName val="7"/>
+      <sheetName val="8"/>
+      <sheetName val="9"/>
+      <sheetName val="10"/>
+      <sheetName val="11"/>
+      <sheetName val="12"/>
+      <sheetName val="13"/>
+      <sheetName val="14"/>
+      <sheetName val="15"/>
+      <sheetName val="16"/>
+      <sheetName val="17"/>
+      <sheetName val="18"/>
+      <sheetName val="19"/>
+      <sheetName val="20"/>
+      <sheetName val="21"/>
+      <sheetName val="22"/>
+      <sheetName val="23"/>
+      <sheetName val="24"/>
+      <sheetName val="25"/>
+      <sheetName val="26"/>
+      <sheetName val="27"/>
+      <sheetName val="28"/>
+      <sheetName val="29"/>
+      <sheetName val="30"/>
+      <sheetName val="31"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="16">
+          <cell r="B16" t="str">
+            <v>KG</v>
+          </cell>
+          <cell r="D16" t="str">
+            <v>Cumalative</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17" t="str">
+            <v>Abseteesm</v>
+          </cell>
+          <cell r="B17">
+            <v>3013.9276666666669</v>
+          </cell>
+          <cell r="D17">
+            <v>0.22884150563122049</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18" t="str">
+            <v>BD Engineering</v>
+          </cell>
+          <cell r="B18">
+            <v>6564.4125000000004</v>
+          </cell>
+          <cell r="D18">
+            <v>0.72726423046914379</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19" t="str">
+            <v>Effeicency loss</v>
+          </cell>
+          <cell r="B19">
+            <v>-44.149066666666798</v>
+          </cell>
+          <cell r="D19">
+            <v>0.72391208005095309</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20" t="str">
+            <v>Mould Breakdown</v>
+          </cell>
+          <cell r="B20">
+            <v>0</v>
+          </cell>
+          <cell r="D20">
+            <v>0.72391208005095309</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21" t="str">
+            <v>Lack of Packing Materials</v>
+          </cell>
+          <cell r="B21">
+            <v>0</v>
+          </cell>
+          <cell r="D21">
+            <v>0.72391208005095309</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22" t="str">
+            <v>Mould Change Delay</v>
+          </cell>
+          <cell r="B22">
+            <v>348.45083333333332</v>
+          </cell>
+          <cell r="D22">
+            <v>0.75036925558982193</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23" t="str">
+            <v>Quality Issues</v>
+          </cell>
+          <cell r="B23">
+            <v>0</v>
+          </cell>
+          <cell r="D23">
+            <v>0.75036925558982193</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24" t="str">
+            <v>Sampling</v>
+          </cell>
+          <cell r="B24">
+            <v>167.04</v>
+          </cell>
+          <cell r="D24">
+            <v>0.76305226902886569</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25" t="str">
+            <v>Machine Settings</v>
+          </cell>
+          <cell r="B25">
+            <v>561.37599999999998</v>
+          </cell>
+          <cell r="D25">
+            <v>0.80567642702908493</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26" t="str">
+            <v>Machine Starting Delay</v>
+          </cell>
+          <cell r="B26">
+            <v>11.9475</v>
+          </cell>
+          <cell r="D26">
+            <v>0.80658357683190451</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27" t="str">
+            <v>Labour Shortage</v>
+          </cell>
+          <cell r="B27">
+            <v>97.2</v>
+          </cell>
+          <cell r="D27">
+            <v>0.81396377861755498</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28" t="str">
+            <v>Power Failure</v>
+          </cell>
+          <cell r="B28">
+            <v>99.325333333333333</v>
+          </cell>
+          <cell r="D28">
+            <v>0.82150535271659808</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29" t="str">
+            <v>Color Changing</v>
+          </cell>
+          <cell r="B29">
+            <v>0</v>
+          </cell>
+          <cell r="D29">
+            <v>0.82150535271659808</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30" t="str">
+            <v>BD Production</v>
+          </cell>
+          <cell r="B30">
+            <v>2188.1274999999996</v>
+          </cell>
+          <cell r="D30">
+            <v>0.98764550171588672</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31" t="str">
+            <v>Hopper Material Stock Taking</v>
+          </cell>
+          <cell r="B31">
+            <v>0</v>
+          </cell>
+          <cell r="D31">
+            <v>0.98764550171588672</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32" t="str">
+            <v>No Orders</v>
+          </cell>
+          <cell r="B32">
+            <v>0</v>
+          </cell>
+          <cell r="D32">
+            <v>0.98764550171588672</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33" t="str">
+            <v>Lack of Materials</v>
+          </cell>
+          <cell r="B33">
+            <v>0</v>
+          </cell>
+          <cell r="D33">
+            <v>0.98764550171588672</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34" t="str">
+            <v>Material Issues</v>
+          </cell>
+          <cell r="B34">
+            <v>0</v>
+          </cell>
+          <cell r="D34">
+            <v>0.98764550171588672</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35" t="str">
+            <v>Planning Delay</v>
+          </cell>
+          <cell r="B35">
+            <v>0</v>
+          </cell>
+          <cell r="D35">
+            <v>0.98764550171588672</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="A36" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="B36">
+            <v>49.866666666666674</v>
+          </cell>
+          <cell r="D36">
+            <v>0.99143177807779792</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="A37" t="str">
+            <v>Early Leave</v>
+          </cell>
+          <cell r="B37">
+            <v>9.7200000000000006</v>
+          </cell>
+          <cell r="D37">
+            <v>0.99216979825636298</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="A38" t="str">
+            <v>Cycle Time Deviation</v>
+          </cell>
+          <cell r="B38">
+            <v>103.12666666666667</v>
+          </cell>
+          <cell r="D38">
+            <v>0.99999999999999989</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
+      <sheetData sheetId="30"/>
+      <sheetData sheetId="31"/>
+      <sheetData sheetId="32"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -611,43 +2455,43 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
@@ -666,11 +2510,11 @@
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -831,43 +2675,43 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
@@ -886,11 +2730,11 @@
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -1051,43 +2895,43 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
@@ -1106,11 +2950,11 @@
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -1271,43 +3115,43 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
@@ -1326,11 +3170,11 @@
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -1491,43 +3335,43 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
@@ -1546,11 +3390,11 @@
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -1711,43 +3555,43 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
@@ -1766,11 +3610,11 @@
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -1931,43 +3775,43 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
@@ -1986,11 +3830,11 @@
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -2151,43 +3995,43 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
@@ -2206,11 +4050,11 @@
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -2371,43 +4215,43 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
@@ -2426,11 +4270,11 @@
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -2591,43 +4435,43 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
@@ -2646,11 +4490,11 @@
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -2811,43 +4655,43 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
@@ -2866,11 +4710,11 @@
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -3031,43 +4875,43 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
@@ -3086,11 +4930,11 @@
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -3251,43 +5095,43 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
@@ -3306,11 +5150,11 @@
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -3471,43 +5315,43 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
@@ -3526,11 +5370,11 @@
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -3691,43 +5535,43 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
@@ -3746,11 +5590,11 @@
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -3911,43 +5755,43 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
@@ -3966,11 +5810,11 @@
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -4131,43 +5975,43 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
@@ -4186,11 +6030,11 @@
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -4351,43 +6195,43 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
@@ -4406,11 +6250,11 @@
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -4571,43 +6415,43 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
@@ -4626,11 +6470,11 @@
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -4791,43 +6635,43 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
@@ -4846,11 +6690,11 @@
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -5011,43 +6855,43 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
@@ -5066,11 +6910,11 @@
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -5231,43 +7075,43 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
@@ -5286,11 +7130,11 @@
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -5451,43 +7295,43 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
@@ -5506,11 +7350,11 @@
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -5671,43 +7515,43 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
@@ -5726,11 +7570,11 @@
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -5891,43 +7735,43 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
@@ -5946,11 +7790,11 @@
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -6098,7 +7942,7 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -6111,43 +7955,43 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
@@ -6166,11 +8010,11 @@
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -6371,12 +8215,12 @@
       </c>
     </row>
     <row r="16" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
@@ -6392,26 +8236,706 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="12" t="e">
+        <f t="shared" ref="B18:B37" si="1">HLOOKUP(A18,$N$3:$AG$6,3,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C18" s="13">
+        <f t="shared" ref="C18:C37" si="2">IFERROR(B18/SUM($B$18:$B$37),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="13">
+        <f>C18</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="12" t="e">
+        <f>HLOOKUP(A19,$N$3:$AG$6,3,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C19" s="13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D19" s="13">
+        <f t="shared" ref="D19:D37" si="3">D18+C19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="12" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C20" s="13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D20" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="12" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C21" s="13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D21" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="12" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C22" s="13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D22" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="12" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C23" s="13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D23" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="12" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C24" s="13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D24" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="12" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C25" s="13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D25" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="12" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C26" s="13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D26" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="12" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C27" s="13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D27" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="12" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C28" s="13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D28" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="12" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C29" s="13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D29" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="12" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C30" s="13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D30" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="12" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C31" s="13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D31" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="12" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C32" s="13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D32" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="12" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C33" s="13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D33" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B34" s="12" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C34" s="13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D34" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B35" s="12" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C35" s="13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D35" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B36" s="12" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C36" s="13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D36" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B37" s="12" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C37" s="13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D37" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
+      <c r="B40" s="15"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B41" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C41" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D41" s="10" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B42" s="12" t="e">
+        <f t="shared" ref="B42:B61" si="4">HLOOKUP(A42,$N$3:$AG$6,4,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C42" s="13">
+        <f t="shared" ref="C42:C61" si="5">IFERROR(B42/SUM($B$42:$B$61),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D42" s="13">
+        <f>C42</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B43" s="12" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C43" s="13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D43" s="13">
+        <f t="shared" ref="D43:D61" si="6">D42+C43</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B44" s="12" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C44" s="13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D44" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B45" s="12" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C45" s="13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D45" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B46" s="12" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C46" s="13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D46" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B47" s="12" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C47" s="13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D47" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B48" s="12" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C48" s="13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D48" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="12" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C49" s="13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D49" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="12" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C50" s="13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D50" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" s="12" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C51" s="13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D51" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B52" s="12" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C52" s="13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D52" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B53" s="12" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C53" s="13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D53" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B54" s="12" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C54" s="13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D54" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B55" s="12" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C55" s="13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D55" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B56" s="12" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C56" s="13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D56" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B57" s="12" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C57" s="13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D57" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B58" s="12" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C58" s="13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D58" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B59" s="12" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C59" s="13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D59" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B60" s="12" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C60" s="13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D60" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B61" s="12" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C61" s="13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D61" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6421,8 +8945,8 @@
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="G3:H3"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A20:D20"/>
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
@@ -6431,6 +8955,7 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6449,43 +8974,43 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
@@ -6504,11 +9029,11 @@
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -6669,43 +9194,43 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
@@ -6724,11 +9249,11 @@
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -6889,43 +9414,43 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
@@ -6944,11 +9469,11 @@
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -7109,43 +9634,43 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
@@ -7164,11 +9689,11 @@
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -7329,43 +9854,43 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
@@ -7384,11 +9909,11 @@
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -7549,43 +10074,43 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
@@ -7604,11 +10129,11 @@
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
